--- a/fft_bins.xlsx
+++ b/fft_bins.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uchile-my.sharepoint.com/personal/bruno_pollarolo_uchile_cl/Documents/Escritorio/Universidad/uchile-ee-thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{B2927232-2800-4DFE-9D2E-776C600784F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A18CEC16-6C19-4424-930C-52F628035842}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="8_{B2927232-2800-4DFE-9D2E-776C600784F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42A3C7E-0033-4518-BCA3-40396F9535D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1E0617D8-6423-4FFD-B40B-AE57EE11F0B1}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>LO (MHz)</t>
   </si>
@@ -443,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00C8E53-EDA0-4925-B592-431A035FE1B0}">
-  <dimension ref="A4:K12"/>
+  <dimension ref="A4:M23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
@@ -452,7 +452,7 @@
     <col min="10" max="10" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -487,7 +487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0</v>
       </c>
@@ -526,7 +526,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -570,7 +570,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -614,7 +614,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -658,7 +658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>4</v>
       </c>
@@ -703,7 +703,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5</v>
       </c>
@@ -748,7 +748,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
@@ -793,7 +793,7 @@
         <v>364.00000000000011</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>7</v>
       </c>
@@ -835,6 +835,402 @@
       <c r="K12" s="1">
         <f t="shared" si="10"/>
         <v>474.00000000000011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s">
+        <v>7</v>
+      </c>
+      <c r="J15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <f>123*8*M16</f>
+        <v>300.29296875</v>
+      </c>
+      <c r="D16">
+        <f>C16+82*8*M16</f>
+        <v>500.48828125</v>
+      </c>
+      <c r="E16">
+        <f>C16/(2500/8192)</f>
+        <v>984</v>
+      </c>
+      <c r="F16">
+        <f>D16/M16</f>
+        <v>1640</v>
+      </c>
+      <c r="G16">
+        <f>E16/8</f>
+        <v>123</v>
+      </c>
+      <c r="H16" s="1">
+        <f>F16/8</f>
+        <v>205</v>
+      </c>
+      <c r="I16">
+        <f>AVERAGE(E16:F16)</f>
+        <v>1312</v>
+      </c>
+      <c r="J16">
+        <f>G16+512</f>
+        <v>635</v>
+      </c>
+      <c r="K16" s="1">
+        <f>512+H16</f>
+        <v>717</v>
+      </c>
+      <c r="M16">
+        <f>2500/8192</f>
+        <v>0.30517578125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f>B17/M$16</f>
+        <v>3496</v>
+      </c>
+      <c r="B17">
+        <f>M16*(3496)</f>
+        <v>1066.89453125</v>
+      </c>
+      <c r="C17">
+        <f>B17-D$16</f>
+        <v>566.40625</v>
+      </c>
+      <c r="D17">
+        <f>B17-C$16</f>
+        <v>766.6015625</v>
+      </c>
+      <c r="E17">
+        <f>C17/M16</f>
+        <v>1856</v>
+      </c>
+      <c r="F17">
+        <f>D17/M16</f>
+        <v>2512</v>
+      </c>
+      <c r="G17">
+        <f t="shared" ref="G17:G23" si="12">E17/8</f>
+        <v>232</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" ref="H17:H23" si="13">F17/8</f>
+        <v>314</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ref="I17:I23" si="14">AVERAGE(E17:F17)</f>
+        <v>2184</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ref="J17:J18" si="15">G17+512</f>
+        <v>744</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" ref="K17:K18" si="16">512+H17</f>
+        <v>826</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" ref="A18:A23" si="17">B18/M$16</f>
+        <v>4368</v>
+      </c>
+      <c r="B18">
+        <f>M16*(8*546)</f>
+        <v>1333.0078125</v>
+      </c>
+      <c r="C18">
+        <f>B18-D$16</f>
+        <v>832.51953125</v>
+      </c>
+      <c r="D18">
+        <f>B18-C$16</f>
+        <v>1032.71484375</v>
+      </c>
+      <c r="E18">
+        <f>C18/M16</f>
+        <v>2728</v>
+      </c>
+      <c r="F18">
+        <f>D18/M16</f>
+        <v>3384</v>
+      </c>
+      <c r="G18">
+        <f>E18/8</f>
+        <v>341</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="13"/>
+        <v>423</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="14"/>
+        <v>3056</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="15"/>
+        <v>853</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="16"/>
+        <v>935</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="17"/>
+        <v>5248</v>
+      </c>
+      <c r="B19">
+        <f>M16*(8*656)</f>
+        <v>1601.5625</v>
+      </c>
+      <c r="C19">
+        <f>B19-D$16</f>
+        <v>1101.07421875</v>
+      </c>
+      <c r="D19">
+        <f>B19-C$16</f>
+        <v>1301.26953125</v>
+      </c>
+      <c r="E19">
+        <f>C19/M16</f>
+        <v>3608</v>
+      </c>
+      <c r="F19">
+        <f>D19/M16</f>
+        <v>4264</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="12"/>
+        <v>451</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="13"/>
+        <v>533</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="14"/>
+        <v>3936</v>
+      </c>
+      <c r="J19" s="1">
+        <f>G19+512</f>
+        <v>963</v>
+      </c>
+      <c r="K19" s="1">
+        <f>H19-512</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="17"/>
+        <v>3496</v>
+      </c>
+      <c r="B20">
+        <f>B17</f>
+        <v>1066.89453125</v>
+      </c>
+      <c r="C20">
+        <f>B20+C$16</f>
+        <v>1367.1875</v>
+      </c>
+      <c r="D20">
+        <f>B20+D$16</f>
+        <v>1567.3828125</v>
+      </c>
+      <c r="E20">
+        <f>C20/M16</f>
+        <v>4480</v>
+      </c>
+      <c r="F20">
+        <f>D20/M16</f>
+        <v>5136</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="12"/>
+        <v>560</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="13"/>
+        <v>642</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="14"/>
+        <v>4808</v>
+      </c>
+      <c r="J20" s="1">
+        <f>G20-512</f>
+        <v>48</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" ref="K20:K23" si="18">H20-512</f>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="17"/>
+        <v>4368</v>
+      </c>
+      <c r="B21">
+        <f>B18</f>
+        <v>1333.0078125</v>
+      </c>
+      <c r="C21">
+        <f>B21+C$16</f>
+        <v>1633.30078125</v>
+      </c>
+      <c r="D21">
+        <f>B21+D$16</f>
+        <v>1833.49609375</v>
+      </c>
+      <c r="E21">
+        <f>C21/M16</f>
+        <v>5352</v>
+      </c>
+      <c r="F21">
+        <f>D21/M16</f>
+        <v>6008</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="12"/>
+        <v>669</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="13"/>
+        <v>751</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="14"/>
+        <v>5680</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" ref="J21:J23" si="19">G21-512</f>
+        <v>157</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="18"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="17"/>
+        <v>5248</v>
+      </c>
+      <c r="B22">
+        <f>B19</f>
+        <v>1601.5625</v>
+      </c>
+      <c r="C22">
+        <f>B22+C$16</f>
+        <v>1901.85546875</v>
+      </c>
+      <c r="D22">
+        <f>B22+D$16</f>
+        <v>2102.05078125</v>
+      </c>
+      <c r="E22">
+        <f>C22/M16</f>
+        <v>6232</v>
+      </c>
+      <c r="F22">
+        <f>D22/M16</f>
+        <v>6888</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="12"/>
+        <v>779</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="13"/>
+        <v>861</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="14"/>
+        <v>6560</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="19"/>
+        <v>267</v>
+      </c>
+      <c r="K22" s="1">
+        <f t="shared" si="18"/>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="17"/>
+        <v>6112</v>
+      </c>
+      <c r="B23">
+        <f>M16*(8*764)</f>
+        <v>1865.234375</v>
+      </c>
+      <c r="C23">
+        <f>B23+C$16</f>
+        <v>2165.52734375</v>
+      </c>
+      <c r="D23">
+        <f>B23+D$16</f>
+        <v>2365.72265625</v>
+      </c>
+      <c r="E23">
+        <f>C23/M16</f>
+        <v>7096</v>
+      </c>
+      <c r="F23">
+        <f>D23/M16</f>
+        <v>7752</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="12"/>
+        <v>887</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="13"/>
+        <v>969</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="14"/>
+        <v>7424</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="19"/>
+        <v>375</v>
+      </c>
+      <c r="K23" s="1">
+        <f t="shared" si="18"/>
+        <v>457</v>
       </c>
     </row>
   </sheetData>

--- a/fft_bins.xlsx
+++ b/fft_bins.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uchile-my.sharepoint.com/personal/bruno_pollarolo_uchile_cl/Documents/Escritorio/Universidad/uchile-ee-thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="233" documentId="8_{B2927232-2800-4DFE-9D2E-776C600784F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42A3C7E-0033-4518-BCA3-40396F9535D7}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="8_{B2927232-2800-4DFE-9D2E-776C600784F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20AD6399-7276-4ABC-AB64-91134E03EFEE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1E0617D8-6423-4FFD-B40B-AE57EE11F0B1}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/fft_bins.xlsx
+++ b/fft_bins.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uchile-my.sharepoint.com/personal/bruno_pollarolo_uchile_cl/Documents/Escritorio/Universidad/uchile-ee-thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{B2927232-2800-4DFE-9D2E-776C600784F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20AD6399-7276-4ABC-AB64-91134E03EFEE}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{B2927232-2800-4DFE-9D2E-776C600784F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA0C5FA-B199-43B6-B43B-5E3BD65C9D92}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1E0617D8-6423-4FFD-B40B-AE57EE11F0B1}"/>
   </bookViews>
